--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="63">
-  <si>
-    <t>Statement: ExerciseService.updateExercise(id, data) – Delegates to exerciseRepository.update(). Propagates NotFoundError if absent. Propagates ConflictError if new name conflicts.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="42">
+  <si>
+    <t>Statement: ExerciseService.updateExercise(id, data)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id: string, data: UpdateExerciseInput (all optional)</t>
+    <t>Input: id, data</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>exerciseRepository is accessible</t>
+    <t>repo accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;Exercise&gt;  OR  throws NotFoundError / ConflictError</t>
+    <t>Output: Exercise</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: updated Exercise returned. On error: no state change.</t>
+    <t>Updated.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,24 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>exercise existence</t>
-  </si>
-  <si>
-    <t>exercise found</t>
-  </si>
-  <si>
-    <t>not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>name uniqueness</t>
-  </si>
-  <si>
-    <t>new name not taken</t>
-  </si>
-  <si>
-    <t>name already taken (ConflictError)</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -97,45 +79,12 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>id exists, { name: "Incline Bench Press" }</t>
-  </si>
-  <si>
-    <t>Returns updated Exercise; update called with (id, data)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>"nonexistent-id", any data</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>id exists, { name: "Squat" } (duplicate)</t>
-  </si>
-  <si>
-    <t>Throws ConflictError</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Name boundaries validated at schema layer</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
@@ -145,25 +94,13 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Existing id, unique new name</t>
-  </si>
-  <si>
-    <t>Returns updated Exercise</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Non-existent id</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Existing id, duplicate name</t>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -721,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -743,62 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -807,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -819,70 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -903,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -943,19 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -966,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -979,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1002,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,19 +861,439 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1082,16 +1321,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1099,45 +1338,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1146,19 +1385,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="42">
-  <si>
-    <t>Statement: ExerciseService.updateExercise(id, data)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="108">
+  <si>
+    <t>Statement: ExerciseService.updateExercise(id, data) – Updates an existing exercise. Returns the updated Exercise on success. Throws NotFoundError if no exercise exists with the given ID. Throws ConflictError if the new name is already in use by another exercise.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id, data</t>
+    <t>Input: id: string, data: UpdateExerciseInput { name?, description?, muscleGroup?, equipmentNeeded? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>repo accessible</t>
+    <t>An exercise with the given ID may or may not exist. The new name may or may not already belong to another exercise.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Exercise</t>
+    <t>Output: Promise&lt;Exercise&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Updated.</t>
+    <t>On success: updated Exercise returned reflecting changed fields. On failure: NotFoundError or ConflictError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,24 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Exercise existence</t>
+  </si>
+  <si>
+    <t>Existing ID → updated Exercise returned</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
+  </si>
+  <si>
+    <t>Name uniqueness</t>
+  </si>
+  <si>
+    <t>Unique name (or name unchanged) → success</t>
+  </si>
+  <si>
+    <t>Name already used by another exercise → ConflictError</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,28 +97,208 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, name: "Updated Bench Press"</t>
+  </si>
+  <si>
+    <t>Exercise returned with name: "Updated Bench Press" and id: EXERCISE_ID</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>id: NONEXISTENT_ID, description: "New description"</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Exercise not found")</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, name: "Existing Exercise"</t>
+  </si>
+  <si>
+    <t>throws ConflictError("Exercise name already in use")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>name field</t>
+  </si>
+  <si>
+    <t>undefined, "" (empty), "a" (1 char)</t>
+  </si>
+  <si>
+    <t>description field</t>
+  </si>
+  <si>
+    <t>muscleGroup field</t>
+  </si>
+  <si>
+    <t>undefined, CHEST, SHOULDERS, ARMS, BACK, CORE, LEGS</t>
+  </si>
+  <si>
+    <t>equipmentNeeded field</t>
+  </si>
+  <si>
+    <t>undefined, CABLE, DUMBBELL, BARBELL, MACHINE</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ""</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match)</t>
+  </si>
+  <si>
+    <t>id: "a" (found), description: "Updated description"</t>
+  </si>
+  <si>
+    <t>Exercise returned with id: "a", description: "Updated description", correct name</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, name: undefined</t>
+  </si>
+  <si>
+    <t>Full Exercise returned (toEqual MOCK_EXERCISE)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, name: ""</t>
+  </si>
+  <si>
+    <t>Exercise returned with name: "" (toEqual expected)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, name: "a"</t>
+  </si>
+  <si>
+    <t>Exercise returned with name: "a" (toEqual expected)</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, description: undefined</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, description: ""</t>
+  </si>
+  <si>
+    <t>Exercise returned with description: "" (toEqual expected)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, description: "a"</t>
+  </si>
+  <si>
+    <t>Exercise returned with description: "a" (toEqual expected)</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: undefined</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: SHOULDERS</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: SHOULDERS</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: ARMS</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: ARMS</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: BACK</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: BACK</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: CORE</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: CORE</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, muscleGroup: LEGS</t>
+  </si>
+  <si>
+    <t>Exercise returned with muscleGroup: LEGS</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, equipmentNeeded: undefined</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, equipmentNeeded: CABLE</t>
+  </si>
+  <si>
+    <t>Exercise returned with equipmentNeeded: CABLE</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, equipmentNeeded: DUMBBELL</t>
+  </si>
+  <si>
+    <t>Exercise returned with equipmentNeeded: DUMBBELL</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, equipmentNeeded: BARBELL</t>
+  </si>
+  <si>
+    <t>Exercise returned with equipmentNeeded: BARBELL</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, equipmentNeeded: MACHINE</t>
+  </si>
+  <si>
+    <t>Exercise returned with equipmentNeeded: MACHINE</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Update</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>Testing</t>
@@ -133,7 +331,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-03</t>
+    <t>SERV-18</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +878,62 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +954,70 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +1038,68 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1122,376 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="B18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="B19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +1515,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1538,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1558,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1578,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1598,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1618,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1638,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1658,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1678,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,19 +1698,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,19 +1718,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,19 +1738,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1758,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,19 +1778,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,19 +1798,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1101,19 +1818,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,19 +1838,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1141,19 +1858,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1161,19 +1878,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1181,19 +1898,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1201,19 +1918,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1221,19 +1938,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,19 +1958,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1261,19 +1978,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,19 +1998,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1321,16 +2038,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1338,39 +2055,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
@@ -1385,19 +2102,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/updateExercise-bbt-form.xlsx
@@ -331,7 +331,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-18</t>
+    <t>SERV-19</t>
   </si>
   <si>
     <t>n/a</t>
